--- a/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-05-2026-10-05.xlsx
+++ b/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-05-2026-10-05.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\SUIVI SERVICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\PROJETS\NOUVEAUX_RECAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{915319A3-68B4-4463-9CE3-1C675165274C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A58B97F-01C7-44C5-B949-13E884D97256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{E2DA8268-CDC1-4ACF-8B87-2BA4C42A3E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{9AE91004-487F-478F-81E8-6738977CB5DD}"/>
   </bookViews>
   <sheets>
     <sheet name="category-sales-summary-2026-10-" sheetId="1" r:id="rId1"/>
@@ -958,7 +958,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFEE7BE-52AE-42DF-9312-9C0661374791}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3097B8E-13A7-4B8B-A019-8890387B3811}">
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
